--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513653_FASEFINALAFFA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513653_FASEFINALAFFA2_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2397</v>
+        <v>5.3264</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9214</v>
+        <v>3.9246</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3183</v>
+        <v>1.4018</v>
       </c>
       <c r="G2" t="n">
         <v>2.9305</v>
@@ -610,13 +610,13 @@
         <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9781</v>
+        <v>1.0648</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3318</v>
+        <v>0.335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6463</v>
+        <v>0.7298</v>
       </c>
       <c r="V2" t="n">
         <v>0.9416</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3461</v>
+        <v>4.2904</v>
       </c>
       <c r="E3" t="n">
         <v>2.4722</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8739</v>
+        <v>1.8183</v>
       </c>
       <c r="G3" t="n">
         <v>1.9353</v>
@@ -688,13 +688,13 @@
         <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6708</v>
+        <v>0.6151</v>
       </c>
       <c r="T3" t="n">
         <v>0.1791</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4917</v>
+        <v>0.4361</v>
       </c>
       <c r="V3" t="n">
         <v>1.9347</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.152</v>
+        <v>4.0848</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3647</v>
+        <v>2.4644</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7873</v>
+        <v>1.6204</v>
       </c>
       <c r="G4" t="n">
         <v>3.645</v>
@@ -766,13 +766,13 @@
         <v>1.3632</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0913</v>
+        <v>1.024</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1883</v>
+        <v>0.288</v>
       </c>
       <c r="U4" t="n">
-        <v>0.903</v>
+        <v>0.736</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6871</v>
+        <v>3.8378</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2003</v>
+        <v>1.1007</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4867</v>
+        <v>2.7372</v>
       </c>
       <c r="G5" t="n">
         <v>3.3059</v>
@@ -844,13 +844,13 @@
         <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>0.238</v>
+        <v>0.3888</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0775</v>
+        <v>-0.1772</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3155</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0516</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0983</v>
+        <v>3.4009</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5747</v>
+        <v>1.7948</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5236</v>
+        <v>1.6062</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9559</v>
+        <v>1.0219</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2735</v>
+        <v>0.6071</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6824</v>
+        <v>0.4148</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1887</v>
+        <v>1.4165</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1642</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0244</v>
+        <v>0.7134</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7672</v>
+        <v>-0.3946</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1093</v>
+        <v>-0.096</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6579</v>
+        <v>-0.2986</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3895</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>0.532</v>
+        <v>0.2164</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1144</v>
+        <v>-0.1486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6464</v>
+        <v>0.365</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2211</v>
+        <v>2.1626</v>
       </c>
       <c r="W6" t="n">
         <v>1.5005</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2795</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0579</v>
+        <v>2.8525</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3961</v>
+        <v>1.7741</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6618</v>
+        <v>1.0784</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0219</v>
+        <v>0.9559</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6071</v>
+        <v>0.2735</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4148</v>
+        <v>0.6824</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4165</v>
+        <v>0.1887</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.1642</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7134</v>
+        <v>0.0244</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3946</v>
+        <v>0.7672</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.096</v>
+        <v>0.1093</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2986</v>
+        <v>0.6579</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9737</v>
+        <v>0.3895</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1266</v>
+        <v>0.2861</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5473</v>
+        <v>0.0849</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4207</v>
+        <v>0.2012</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1626</v>
+        <v>1.2211</v>
       </c>
       <c r="W7" t="n">
         <v>1.5005</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6621</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9422</v>
+        <v>2.3804</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2074</v>
+        <v>0.0916</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1496</v>
+        <v>2.2888</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5079</v>
@@ -1078,13 +1078,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2967</v>
+        <v>0.1414</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4328</v>
+        <v>-0.1338</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1361</v>
+        <v>0.2753</v>
       </c>
       <c r="V8" t="n">
         <v>2.1626</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2316</v>
+        <v>1.6423</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2316</v>
+        <v>-0.732</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.3744</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2316</v>
+        <v>0.8325</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2316</v>
+        <v>0.6722</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.1603</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2316</v>
+        <v>-0.4598</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2316</v>
+        <v>0.1642</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.624</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.2922</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.508</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.7843</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.0309</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.2722</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.3032</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9654</v>
+        <v>1.2316</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1307</v>
+        <v>1.2316</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0961</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8325</v>
+        <v>1.2316</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6722</v>
+        <v>1.2316</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1603</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4598</v>
+        <v>1.2316</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1642</v>
+        <v>1.2316</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.624</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2922</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.508</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7843</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.646</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.671</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0249</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3864</v>
+        <v>-1.1443</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0707</v>
+        <v>-1.9678</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6844</v>
+        <v>0.8235</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6445</v>
@@ -1312,13 +1312,13 @@
         <v>0.9737</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9008</v>
+        <v>1.1428</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4555</v>
+        <v>0.5584</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4453</v>
+        <v>0.5844</v>
       </c>
       <c r="V11" t="n">
         <v>0.3311</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3784</v>
+        <v>-1.4665</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2737</v>
+        <v>-2.4731</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8953</v>
+        <v>1.0066</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4263</v>
@@ -1390,13 +1390,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6584</v>
+        <v>0.5704</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4975</v>
+        <v>0.2981</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1609</v>
+        <v>0.2722</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2211</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4553</v>
+        <v>-2.2474</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.457</v>
+        <v>-3.0536</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0017</v>
+        <v>0.8062</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1701</v>
+        <v>-2.9846</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9853</v>
+        <v>-0.3069</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1848</v>
+        <v>-2.6777</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.8649</v>
+        <v>-2.3965</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.549</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2415</v>
+        <v>-1.8475</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6948</v>
+        <v>-0.5881</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3618</v>
+        <v>0.2422</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0566</v>
+        <v>-0.8302</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9737</v>
+        <v>0.7789</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0527</v>
+        <v>0.9319</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6183</v>
+        <v>0.3166</v>
       </c>
       <c r="U13" t="n">
-        <v>0.671</v>
+        <v>0.6153</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.8176</v>
+        <v>-2.5064</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.6517</v>
+        <v>-5.2576</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8341</v>
+        <v>2.7512</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.9846</v>
+        <v>-3.1701</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3069</v>
+        <v>-0.9853</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.6777</v>
+        <v>-2.1848</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3965</v>
+        <v>-3.8649</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.549</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8475</v>
+        <v>-3.2415</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5881</v>
+        <v>0.6948</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2422</v>
+        <v>-0.3618</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8302</v>
+        <v>1.0566</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3617</v>
+        <v>0.0016</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2815</v>
+        <v>-0.419</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6432</v>
+        <v>0.4206</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="15">
@@ -1579,25 +1579,25 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>21.6826</v>
+        <v>21.6825</v>
       </c>
       <c r="E15" t="n">
-        <v>1.369800000000001</v>
+        <v>1.369899999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>20.3128</v>
+        <v>20.313</v>
       </c>
       <c r="G15" t="n">
-        <v>7.1252</v>
+        <v>7.125200000000001</v>
       </c>
       <c r="H15" t="n">
         <v>1.1447</v>
       </c>
       <c r="I15" t="n">
-        <v>5.980600000000001</v>
+        <v>5.9806</v>
       </c>
       <c r="J15" t="n">
-        <v>3.058000000000001</v>
+        <v>3.058000000000002</v>
       </c>
       <c r="K15" t="n">
         <v>0.8348000000000008</v>
@@ -1612,7 +1612,7 @@
         <v>0.3101</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7573</v>
+        <v>3.757300000000001</v>
       </c>
       <c r="P15" t="n">
         <v>2.775557561562891e-17</v>
@@ -1624,13 +1624,13 @@
         <v>10.7105</v>
       </c>
       <c r="S15" t="n">
-        <v>6.4145</v>
+        <v>6.4142</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9094000000000001</v>
+        <v>0.9093</v>
       </c>
       <c r="U15" t="n">
-        <v>5.505</v>
+        <v>5.505100000000001</v>
       </c>
       <c r="V15" t="n">
         <v>8.1431</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7482</v>
+        <v>2.7266</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1674</v>
+        <v>1.7687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5808</v>
+        <v>0.9579</v>
       </c>
       <c r="G16" t="n">
         <v>1.872</v>
@@ -1702,13 +1702,13 @@
         <v>1.1684</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1144</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2778</v>
+        <v>-0.1209</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3707</v>
+        <v>0.0064</v>
       </c>
       <c r="V16" t="n">
         <v>2.7216</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.129</v>
+        <v>0.4728</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1697</v>
+        <v>0.2694</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0408</v>
+        <v>0.2034</v>
       </c>
       <c r="G17" t="n">
         <v>1.0158</v>
@@ -1780,13 +1780,13 @@
         <v>0.9737</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9705</v>
+        <v>-0.6267</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5565</v>
+        <v>-0.4568</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.414</v>
+        <v>-0.1698</v>
       </c>
       <c r="V17" t="n">
         <v>-0.89</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9639</v>
+        <v>-0.2878</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0566</v>
+        <v>-0.7575</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0926</v>
+        <v>0.4697</v>
       </c>
       <c r="G18" t="n">
         <v>0.1303</v>
@@ -1858,13 +1858,13 @@
         <v>1.5579</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6784</v>
+        <v>-1.0023</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1749</v>
+        <v>-0.8758</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5036</v>
+        <v>-0.1265</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9833</v>
+        <v>-0.4122</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.801</v>
+        <v>-0.502</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1822</v>
+        <v>0.0898</v>
       </c>
       <c r="G19" t="n">
         <v>0.145</v>
@@ -1936,13 +1936,13 @@
         <v>1.9474</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8546</v>
+        <v>-1.2836</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2367</v>
+        <v>-0.9377</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6179</v>
+        <v>-0.3459</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2211</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ELOLA AGUIRREZABALA</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4989</v>
+        <v>-1.1324</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7354000000000001</v>
+        <v>0.8167</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7634</v>
+        <v>-1.9491</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9865</v>
+        <v>0.3611</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5455</v>
+        <v>1.0274</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.441</v>
+        <v>-0.6663</v>
       </c>
       <c r="J20" t="n">
-        <v>0.066</v>
+        <v>1.6307</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08210000000000001</v>
+        <v>1.6063</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0161</v>
+        <v>0.0244</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0526</v>
+        <v>-1.2696</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6276</v>
+        <v>-0.5789</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4249</v>
+        <v>-0.6907</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1761</v>
+        <v>-0.6871</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1393</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3154</v>
+        <v>0.1269</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2726</v>
+        <v>-1.78</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6105</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>P. ELOLA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5087</v>
+        <v>-1.5545</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5177</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0263</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3611</v>
+        <v>-0.9865</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0274</v>
+        <v>-0.5455</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6663</v>
+        <v>-0.441</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6307</v>
+        <v>0.066</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6063</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0244</v>
+        <v>-0.0161</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2696</v>
+        <v>-1.0526</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5789</v>
+        <v>-0.6276</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6907</v>
+        <v>-0.4249</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9737</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9737</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0634</v>
+        <v>0.1204</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>-0.1393</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0496</v>
+        <v>0.2598</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.78</v>
+        <v>-1.2726</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.78</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>X. OSTOLAZA OSTOLAZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5541</v>
+        <v>-1.6262</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2983</v>
+        <v>-0.7644</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7442</v>
+        <v>-0.8618</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4534</v>
+        <v>-0.8223</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6363</v>
+        <v>0.1795</v>
       </c>
       <c r="I22" t="n">
-        <v>0.183</v>
+        <v>-1.0018</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1693</v>
+        <v>-0.5013</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3719</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2026</v>
+        <v>-0.5835</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2841</v>
+        <v>-0.321</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2644</v>
+        <v>0.0974</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0197</v>
+        <v>-0.4184</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1947</v>
+        <v>0.1947</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8008</v>
+        <v>0.2224</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4485</v>
+        <v>-0.263</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2493</v>
+        <v>0.4854</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7068</v>
+        <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.7068</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. OSTOLAZA OSTOLAZA</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.892</v>
+        <v>-2.028</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7644</v>
+        <v>-3.398</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1276</v>
+        <v>1.37</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8223</v>
+        <v>-0.4534</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1795</v>
+        <v>-0.6363</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0018</v>
+        <v>0.183</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5013</v>
+        <v>-0.1693</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.3719</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5835</v>
+        <v>0.2026</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.321</v>
+        <v>-0.2841</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0974</v>
+        <v>-0.2644</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4184</v>
+        <v>-0.0197</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1947</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1947</v>
+        <v>0.7789</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0434</v>
+        <v>0.3269</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.263</v>
+        <v>-0.5482</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2196</v>
+        <v>0.8751</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2211</v>
+        <v>-1.7068</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.7068</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1662</v>
+        <v>-3.5146</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0345</v>
+        <v>-3.7322</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1317</v>
+        <v>0.2176</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1979</v>
@@ -2326,13 +2326,13 @@
         <v>0.9737</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1114</v>
+        <v>-0.4598</v>
       </c>
       <c r="T24" t="n">
-        <v>0.587</v>
+        <v>-0.1107</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6984</v>
+        <v>-0.3491</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8832</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3238</v>
+        <v>-5.1631</v>
       </c>
       <c r="E25" t="n">
         <v>-6.3634</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0396</v>
+        <v>1.2003</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8293</v>
@@ -2404,13 +2404,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1577</v>
+        <v>0.003</v>
       </c>
       <c r="T25" t="n">
         <v>-0.263</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1053</v>
+        <v>0.266</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.6689</v>
+        <v>-7.1697</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.1139</v>
+        <v>-6.9145</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.555</v>
+        <v>-0.2551</v>
       </c>
       <c r="G26" t="n">
         <v>-5.36</v>
@@ -2482,13 +2482,13 @@
         <v>0.9737</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4189</v>
+        <v>-0.9197</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1749</v>
+        <v>-0.9755</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.244</v>
+        <v>0.0558</v>
       </c>
       <c r="V26" t="n">
         <v>-0.89</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.6826</v>
+        <v>-19.6891</v>
       </c>
       <c r="E27" t="n">
-        <v>-20.3127</v>
+        <v>-20.3126</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3698</v>
+        <v>0.6235999999999998</v>
       </c>
       <c r="G27" t="n">
         <v>-7.1252</v>
@@ -2560,13 +2560,13 @@
         <v>10.7105</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.414199999999999</v>
+        <v>-4.4209</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.505</v>
+        <v>-5.504899999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9094</v>
+        <v>1.0841</v>
       </c>
       <c r="V27" t="n">
         <v>-8.1432</v>
